--- a/Result/profitability/3311.xlsx
+++ b/Result/profitability/3311.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.45</v>
       </c>
       <c r="M2" t="n">
-        <v>0.46875</v>
+        <v>0.585</v>
       </c>
       <c r="N2" t="n">
-        <v>13.36125</v>
+        <v>13.60875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -693,7 +693,7 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
         <v>97.09999999999999</v>
@@ -780,10 +780,10 @@
         <v>1.83</v>
       </c>
       <c r="M3" t="n">
-        <v>0.76625</v>
+        <v>0.7350000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>15.25</v>
+        <v>15.255</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -804,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
         <v>97.2</v>
@@ -899,10 +899,10 @@
         <v>1.92</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9275</v>
+        <v>0.90625</v>
       </c>
       <c r="N4" t="n">
-        <v>16.8</v>
+        <v>16.5775</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="n">
         <v>97.3</v>
@@ -1018,10 +1018,10 @@
         <v>1.73</v>
       </c>
       <c r="M5" t="n">
-        <v>1.075</v>
+        <v>1.1075</v>
       </c>
       <c r="N5" t="n">
-        <v>17.53875</v>
+        <v>17.3625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.88</v>
       </c>
       <c r="M6" t="n">
-        <v>1.185</v>
+        <v>1.16</v>
       </c>
       <c r="N6" t="n">
-        <v>18.49625</v>
+        <v>18.34375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.83</v>
       </c>
       <c r="M7" t="n">
-        <v>1.345</v>
+        <v>1.31125</v>
       </c>
       <c r="N7" t="n">
-        <v>19.67625</v>
+        <v>19.49</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>2.47</v>
       </c>
       <c r="M8" t="n">
-        <v>1.57625</v>
+        <v>1.5575</v>
       </c>
       <c r="N8" t="n">
-        <v>21.15625</v>
+        <v>21.1475</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9360,19 +9360,19 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>-11</v>
+        <v>-3</v>
       </c>
       <c r="J71" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M71" t="n">
-        <v>0.28625</v>
+        <v>0.30125</v>
       </c>
       <c r="N71" t="n">
         <v>12.8425</v>
@@ -9402,10 +9402,10 @@
         <v>114.2</v>
       </c>
       <c r="W71" t="n">
-        <v>-0.55</v>
+        <v>-0.43</v>
       </c>
       <c r="X71" t="n">
-        <v>-1</v>
+        <v>-0.7818181818181819</v>
       </c>
       <c r="Y71" t="n">
         <v>-0.3699999999999992</v>
@@ -9414,10 +9414,10 @@
         <v>-0.02897415818324189</v>
       </c>
       <c r="AA71" t="n">
-        <v>-0.4</v>
+        <v>-0.28</v>
       </c>
       <c r="AB71" t="n">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
       <c r="AC71" t="n">
         <v>-1.17</v>
@@ -9487,19 +9487,19 @@
         </is>
       </c>
       <c r="I72" t="n">
+        <v>31</v>
+      </c>
+      <c r="J72" t="n">
         <v>39</v>
       </c>
-      <c r="J72" t="n">
-        <v>47</v>
-      </c>
       <c r="K72" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="L72" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="M72" t="n">
-        <v>0.29</v>
+        <v>0.29375</v>
       </c>
       <c r="N72" t="n">
         <v>12.39625</v>
@@ -9529,12 +9529,10 @@
         <v>114.3</v>
       </c>
       <c r="W72" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.34</v>
+      </c>
+      <c r="X72" t="n">
+        <v>2.833333333333333</v>
       </c>
       <c r="Y72" t="n">
         <v>-0.1899999999999995</v>
@@ -9543,10 +9541,10 @@
         <v>-0.01532258064516123</v>
       </c>
       <c r="AA72" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AB72" t="n">
-        <v>-2</v>
+        <v>-1.836363636363636</v>
       </c>
       <c r="AC72" t="n">
         <v>3.200000000000001</v>
@@ -9628,7 +9626,7 @@
         <v>0.62</v>
       </c>
       <c r="M73" t="n">
-        <v>0.3175</v>
+        <v>0.32125</v>
       </c>
       <c r="N73" t="n">
         <v>12.1075</v>
@@ -9658,10 +9656,10 @@
         <v>114.4</v>
       </c>
       <c r="W73" t="n">
-        <v>0.06999999999999995</v>
+        <v>0.16</v>
       </c>
       <c r="X73" t="n">
-        <v>0.1272727272727272</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="Y73" t="n">
         <v>0.2699999999999996</v>
@@ -9755,7 +9753,7 @@
         <v>0.5</v>
       </c>
       <c r="M74" t="n">
-        <v>0.3375</v>
+        <v>0.34125</v>
       </c>
       <c r="N74" t="n">
         <v>11.80625</v>
@@ -9836,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3311</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>657</v>
+      </c>
+      <c r="D75" t="n">
+        <v>585</v>
+      </c>
+      <c r="E75" t="n">
+        <v>72</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>34</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34</v>
+      </c>
+      <c r="K75" t="n">
+        <v>35</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="N75" t="n">
+        <v>11.48375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.07000000000000028</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.006329113924050667</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.916666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1137096774193549</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
